--- a/ResourcesBD/ProductEnrichmentComponentApproval.xlsx
+++ b/ResourcesBD/ProductEnrichmentComponentApproval.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7350"/>
   </bookViews>
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="33">
   <si>
     <t>Product ID</t>
   </si>
@@ -51,13 +51,13 @@
     <t>Approval Status</t>
   </si>
   <si>
-    <t>20300049</t>
+    <t>67378491</t>
   </si>
   <si>
     <t>1532</t>
   </si>
   <si>
-    <t>KNORR SOUP CHICKEN &amp; MUSHROOM 12X43G</t>
+    <t>DOVE ENV DFNC SAMPO DETOX 200TK 24X180ML</t>
   </si>
   <si>
     <t>Y</t>
@@ -66,7 +66,55 @@
     <t>NCP</t>
   </si>
   <si>
-    <t>Test</t>
+    <t>3305.10.00</t>
+  </si>
+  <si>
+    <t>69583769</t>
+  </si>
+  <si>
+    <t>LIFEBUOY LQ HW LEMON FR 350TK 12X1L</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>64792125</t>
+  </si>
+  <si>
+    <t>LIFEBUOY LQ HW CR MES YY JP 75T 24X170ML</t>
+  </si>
+  <si>
+    <t>69619574</t>
+  </si>
+  <si>
+    <t>LIFEBUOY SKN BAR CARE JPPCR 68TK 72X150G</t>
+  </si>
+  <si>
+    <t>69717899</t>
+  </si>
+  <si>
+    <t>SUNSILK SHMP PS 420K CND CP 24X340ML</t>
+  </si>
+  <si>
+    <t>69617448</t>
+  </si>
+  <si>
+    <t>SUNSILK SHMP T&amp;L JUL 24X170ML</t>
+  </si>
+  <si>
+    <t>64770091</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BAR TOTAL 50TK RL 72X100G</t>
+  </si>
+  <si>
+    <t>68701895</t>
+  </si>
+  <si>
+    <t>VIM HDW STD LIQUID PRO 55TK 24X250ML</t>
   </si>
   <si>
     <t>0000.00.00</t>
@@ -388,11 +436,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="13.7265625" customWidth="1"/>
-    <col min="9" max="9" width="13.08984375" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -438,7 +494,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -453,10 +509,234 @@
         <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
